--- a/data/trans_bre/IP17-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IP17-Provincia-trans_bre.xlsx
@@ -602,7 +602,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -660,49 +660,49 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-14,03; 11,29</t>
+          <t>-13,66; 11,64</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-18,75; 7,1</t>
+          <t>-19,64; 7,45</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-14,81; 12,42</t>
+          <t>-12,99; 12,94</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-12,18; 9,19</t>
+          <t>-11,14; 9,05</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-47,25; 62,02</t>
+          <t>-45,64; 61,88</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-51,34; 32,52</t>
+          <t>-55,59; 34,18</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-41,93; 63,43</t>
+          <t>-37,93; 62,45</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-53,03; 69,05</t>
+          <t>-50,18; 74,37</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -760,49 +760,49 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-13,71; 1,78</t>
+          <t>-13,5; 1,65</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-11,15; 8,76</t>
+          <t>-10,57; 9,63</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-9,28; 10,77</t>
+          <t>-8,51; 11,7</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-10,68; 5,17</t>
+          <t>-11,14; 6,6</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-64,15; 15,32</t>
+          <t>-61,42; 14,81</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-36,06; 38,26</t>
+          <t>-33,86; 43,04</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-30,44; 50,65</t>
+          <t>-28,02; 55,3</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-64,82; 52,08</t>
+          <t>-64,5; 64,34</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-14,72; 9,31</t>
+          <t>-15,9; 9,22</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-12,7; 12,88</t>
+          <t>-12,56; 13,21</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-11,19; 9,8</t>
+          <t>-8,62; 10,17</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-12,06; 12,44</t>
+          <t>-13,24; 11,07</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-47,21; 49,17</t>
+          <t>-49,11; 47,06</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-36,16; 57,57</t>
+          <t>-34,38; 59,15</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-57,66; 112,67</t>
+          <t>-52,16; 129,08</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-40,06; 73,2</t>
+          <t>-45,41; 64,57</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-10,58; 11,0</t>
+          <t>-10,65; 11,51</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-6,78; 15,08</t>
+          <t>-6,82; 15,63</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-13,09; 11,08</t>
+          <t>-12,98; 11,76</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-13,6; 15,92</t>
+          <t>-13,77; 12,91</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-35,32; 59,65</t>
+          <t>-35,81; 60,09</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-27,6; 93,99</t>
+          <t>-27,92; 111,57</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-34,44; 44,45</t>
+          <t>-35,37; 49,06</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-50,89; 175,21</t>
+          <t>-50,44; 124,03</t>
         </is>
       </c>
     </row>
@@ -1060,49 +1060,49 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-9,01; 17,25</t>
+          <t>-8,02; 17,7</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-12,22; 18,4</t>
+          <t>-12,88; 20,25</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-12,86; 16,6</t>
+          <t>-11,57; 16,85</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-13,19; 10,39</t>
+          <t>-12,18; 11,09</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-47,65; 228,87</t>
+          <t>-44,97; 233,94</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-38,48; 101,26</t>
+          <t>-40,83; 120,94</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-46,52; 124,52</t>
+          <t>-42,33; 105,47</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-69,32; 164,02</t>
+          <t>-68,65; 149,79</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1160,49 +1160,49 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-6,16; 15,74</t>
+          <t>-6,67; 16,29</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-10,49; 15,9</t>
+          <t>-10,4; 17,45</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-11,35; 15,34</t>
+          <t>-8,44; 16,51</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-23,2; 3,08</t>
+          <t>-23,34; 2,59</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-30,64; 140,13</t>
+          <t>-30,9; 151,79</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-33,49; 85,25</t>
+          <t>-33,81; 94,67</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-41,58; 118,64</t>
+          <t>-33,97; 143,89</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-62,66; 14,04</t>
+          <t>-64,93; 14,96</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-10,96; 6,58</t>
+          <t>-11,23; 5,88</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-8,98; 6,97</t>
+          <t>-9,31; 6,55</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-7,52; 4,01</t>
+          <t>-6,31; 4,34</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-8,27; 9,1</t>
+          <t>-8,02; 9,59</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-33,81; 29,04</t>
+          <t>-33,94; 25,74</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-33,15; 36,35</t>
+          <t>-35,26; 33,56</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-57,82; 66,33</t>
+          <t>-53,92; 69,03</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-38,55; 73,87</t>
+          <t>-38,36; 69,8</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-15,36; -1,69</t>
+          <t>-14,74; -1,95</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-5,21; 7,29</t>
+          <t>-5,45; 6,97</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-3,94; 9,53</t>
+          <t>-3,9; 9,72</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-9,5; 2,01</t>
+          <t>-10,26; 2,01</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-58,96; -7,82</t>
+          <t>-56,81; -9,33</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-32,06; 65,29</t>
+          <t>-32,92; 65,38</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-18,64; 64,75</t>
+          <t>-18,19; 62,19</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-60,21; 23,48</t>
+          <t>-62,44; 23,23</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-6,45; 0,3</t>
+          <t>-6,5; 0,45</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,79; 3,81</t>
+          <t>-3,56; 3,89</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-2,61; 4,43</t>
+          <t>-2,71; 4,1</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-6,25; 1,19</t>
+          <t>-6,11; 1,53</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-26,75; 1,41</t>
+          <t>-26,78; 2,8</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-15,18; 18,17</t>
+          <t>-14,3; 18,47</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-12,18; 25,54</t>
+          <t>-12,32; 22,8</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-32,34; 8,15</t>
+          <t>-31,29; 10,46</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP17-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IP17-Provincia-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-13,66; 11,64</t>
+          <t>-12,77; 12,32</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-19,64; 7,45</t>
+          <t>-19,09; 7,58</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-12,99; 12,94</t>
+          <t>-14,26; 11,89</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-11,14; 9,05</t>
+          <t>-12,21; 9,57</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-45,64; 61,88</t>
+          <t>-40,91; 70,29</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-55,59; 34,18</t>
+          <t>-52,27; 33,22</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-37,93; 62,45</t>
+          <t>-40,9; 56,33</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-50,18; 74,37</t>
+          <t>-52,54; 76,01</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-13,5; 1,65</t>
+          <t>-12,68; 1,84</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-10,57; 9,63</t>
+          <t>-9,12; 10,08</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-8,51; 11,7</t>
+          <t>-7,29; 10,87</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-11,14; 6,6</t>
+          <t>-12,22; 5,46</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-61,42; 14,81</t>
+          <t>-60,78; 14,76</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-33,86; 43,04</t>
+          <t>-29,01; 46,68</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-28,02; 55,3</t>
+          <t>-25,52; 51,75</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-64,5; 64,34</t>
+          <t>-69,28; 57,19</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-15,9; 9,22</t>
+          <t>-16,4; 7,93</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-12,56; 13,21</t>
+          <t>-12,29; 13,15</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-8,62; 10,17</t>
+          <t>-8,93; 9,53</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-13,24; 11,07</t>
+          <t>-13,99; 10,56</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-49,11; 47,06</t>
+          <t>-50,13; 36,66</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-34,38; 59,15</t>
+          <t>-33,69; 59,54</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-52,16; 129,08</t>
+          <t>-52,92; 127,66</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-45,41; 64,57</t>
+          <t>-44,96; 57,89</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-10,65; 11,51</t>
+          <t>-9,96; 12,02</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-6,82; 15,63</t>
+          <t>-7,59; 15,3</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-12,98; 11,76</t>
+          <t>-12,43; 12,76</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-13,77; 12,91</t>
+          <t>-14,39; 13,29</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-35,81; 60,09</t>
+          <t>-33,46; 66,71</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-27,92; 111,57</t>
+          <t>-29,33; 98,67</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-35,37; 49,06</t>
+          <t>-33,59; 55,54</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-50,44; 124,03</t>
+          <t>-56,04; 129,46</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-8,02; 17,7</t>
+          <t>-8,34; 16,78</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-12,88; 20,25</t>
+          <t>-12,71; 18,15</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-11,57; 16,85</t>
+          <t>-14,1; 16,52</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-12,18; 11,09</t>
+          <t>-13,71; 8,89</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-44,97; 233,94</t>
+          <t>-45,13; 228,62</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-40,83; 120,94</t>
+          <t>-41,22; 109,0</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-42,33; 105,47</t>
+          <t>-46,78; 111,85</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-68,65; 149,79</t>
+          <t>-75,89; 121,41</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-6,67; 16,29</t>
+          <t>-7,13; 16,19</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-10,4; 17,45</t>
+          <t>-10,94; 16,18</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-8,44; 16,51</t>
+          <t>-10,41; 15,54</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-23,34; 2,59</t>
+          <t>-24,1; 3,17</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-30,9; 151,79</t>
+          <t>-37,84; 148,82</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-33,81; 94,67</t>
+          <t>-34,42; 78,15</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-33,97; 143,89</t>
+          <t>-40,19; 127,55</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-64,93; 14,96</t>
+          <t>-64,68; 14,42</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-11,23; 5,88</t>
+          <t>-10,44; 6,42</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-9,31; 6,55</t>
+          <t>-9,16; 7,57</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-6,31; 4,34</t>
+          <t>-6,49; 4,17</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-8,02; 9,59</t>
+          <t>-7,88; 9,61</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-33,94; 25,74</t>
+          <t>-33,67; 26,9</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-35,26; 33,56</t>
+          <t>-33,95; 39,27</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-53,92; 69,03</t>
+          <t>-55,26; 66,29</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-38,36; 69,8</t>
+          <t>-36,82; 67,98</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-14,74; -1,95</t>
+          <t>-14,24; -1,04</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-5,45; 6,97</t>
+          <t>-5,56; 7,15</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-3,9; 9,72</t>
+          <t>-3,85; 9,88</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-10,26; 2,01</t>
+          <t>-9,88; 2,17</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-56,81; -9,33</t>
+          <t>-56,5; -5,17</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-32,92; 65,38</t>
+          <t>-32,08; 67,57</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-18,19; 62,19</t>
+          <t>-18,24; 65,47</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-62,44; 23,23</t>
+          <t>-59,23; 24,94</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-6,5; 0,45</t>
+          <t>-6,11; 0,94</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,56; 3,89</t>
+          <t>-3,24; 4,44</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-2,71; 4,1</t>
+          <t>-2,62; 4,06</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-6,11; 1,53</t>
+          <t>-5,76; 1,16</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-26,78; 2,8</t>
+          <t>-25,52; 4,47</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-14,3; 18,47</t>
+          <t>-13,53; 22,1</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-12,32; 22,8</t>
+          <t>-12,8; 22,07</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-31,29; 10,46</t>
+          <t>-30,44; 7,61</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP17-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IP17-Provincia-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han necesitado consulta del médico en las últimas 2 semanas</t>
+          <t>Menores que han necesitado consulta médica en las últimas 2 semanas</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-1,22</t>
+          <t>0,69</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-6,89%</t>
+          <t>3,61%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-12,77; 12,32</t>
+          <t>-14,03; 11,29</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-19,09; 7,58</t>
+          <t>-18,75; 7,1</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-14,26; 11,89</t>
+          <t>-14,81; 12,42</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-12,21; 9,57</t>
+          <t>-11,11; 11,74</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-40,91; 70,29</t>
+          <t>-47,25; 62,02</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-52,27; 33,22</t>
+          <t>-51,34; 32,52</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-40,9; 56,33</t>
+          <t>-41,93; 63,43</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-52,54; 76,01</t>
+          <t>-44,34; 91,65</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-2,05</t>
+          <t>0,59</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-16,05%</t>
+          <t>4,76%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-12,68; 1,84</t>
+          <t>-13,71; 1,78</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-9,12; 10,08</t>
+          <t>-11,15; 8,76</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-7,29; 10,87</t>
+          <t>-9,28; 10,77</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-12,22; 5,46</t>
+          <t>-6,77; 8,48</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-60,78; 14,76</t>
+          <t>-64,15; 15,32</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-29,01; 46,68</t>
+          <t>-36,06; 38,26</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-25,52; 51,75</t>
+          <t>-30,44; 50,65</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-69,28; 57,19</t>
+          <t>-43,22; 95,15</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-0,5</t>
+          <t>0,34</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-2,04%</t>
+          <t>1,46%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-16,4; 7,93</t>
+          <t>-14,72; 9,31</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-12,29; 13,15</t>
+          <t>-12,7; 12,88</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-8,93; 9,53</t>
+          <t>-11,19; 9,8</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-13,99; 10,56</t>
+          <t>-10,98; 12,83</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-50,13; 36,66</t>
+          <t>-47,21; 49,17</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-33,69; 59,54</t>
+          <t>-36,16; 57,57</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-52,92; 127,66</t>
+          <t>-57,66; 112,67</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-44,96; 57,89</t>
+          <t>-37,6; 85,6</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0,11</t>
+          <t>-0,63</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>-3,27%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-9,96; 12,02</t>
+          <t>-10,58; 11,0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-7,59; 15,3</t>
+          <t>-6,78; 15,08</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-12,43; 12,76</t>
+          <t>-13,09; 11,08</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-14,39; 13,29</t>
+          <t>-14,89; 14,61</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-33,46; 66,71</t>
+          <t>-35,32; 59,65</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-29,33; 98,67</t>
+          <t>-27,6; 93,99</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-33,59; 55,54</t>
+          <t>-34,44; 44,45</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-56,04; 129,46</t>
+          <t>-54,32; 145,39</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-1,66</t>
+          <t>-1,67</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-12,61%</t>
+          <t>-12,29%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-8,34; 16,78</t>
+          <t>-9,01; 17,25</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-12,71; 18,15</t>
+          <t>-12,22; 18,4</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-14,1; 16,52</t>
+          <t>-12,86; 16,6</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-13,71; 8,89</t>
+          <t>-13,81; 10,57</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-45,13; 228,62</t>
+          <t>-47,65; 228,87</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-41,22; 109,0</t>
+          <t>-38,48; 101,26</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-46,78; 111,85</t>
+          <t>-46,52; 124,52</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-75,89; 121,41</t>
+          <t>-70,81; 155,92</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-10,57</t>
+          <t>-9,9</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>-34,83%</t>
+          <t>-33,44%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-7,13; 16,19</t>
+          <t>-6,16; 15,74</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-10,94; 16,18</t>
+          <t>-10,49; 15,9</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-10,41; 15,54</t>
+          <t>-11,35; 15,34</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-24,1; 3,17</t>
+          <t>-22,88; 3,79</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-37,84; 148,82</t>
+          <t>-30,64; 140,13</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-34,42; 78,15</t>
+          <t>-33,49; 85,25</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-40,19; 127,55</t>
+          <t>-41,58; 118,64</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-64,68; 14,42</t>
+          <t>-62,89; 17,47</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>0,13</t>
+          <t>-3,51</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>-17,8%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-10,44; 6,42</t>
+          <t>-10,96; 6,58</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-9,16; 7,57</t>
+          <t>-8,98; 6,97</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-6,49; 4,17</t>
+          <t>-7,52; 4,01</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-7,88; 9,61</t>
+          <t>-11,34; 4,27</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-33,67; 26,9</t>
+          <t>-33,81; 29,04</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-33,95; 39,27</t>
+          <t>-33,15; 36,35</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-55,26; 66,29</t>
+          <t>-57,82; 66,33</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-36,82; 67,98</t>
+          <t>-47,47; 30,33</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>-3,62</t>
+          <t>-4,09</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>-28,45%</t>
+          <t>-33,52%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-14,24; -1,04</t>
+          <t>-15,36; -1,69</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-5,56; 7,15</t>
+          <t>-5,21; 7,29</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-3,85; 9,88</t>
+          <t>-3,94; 9,53</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-9,88; 2,17</t>
+          <t>-9,98; 1,15</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-56,5; -5,17</t>
+          <t>-58,96; -7,82</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-32,08; 67,57</t>
+          <t>-32,06; 65,29</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-18,24; 65,47</t>
+          <t>-18,64; 64,75</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-59,23; 24,94</t>
+          <t>-63,38; 14,22</t>
         </is>
       </c>
     </row>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>-2,19</t>
+          <t>-2,18</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>-12,7%</t>
+          <t>-12,55%</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-6,11; 0,94</t>
+          <t>-6,45; 0,3</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,24; 4,44</t>
+          <t>-3,79; 3,81</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-2,62; 4,06</t>
+          <t>-2,61; 4,43</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-5,76; 1,16</t>
+          <t>-6,0; 0,93</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-25,52; 4,47</t>
+          <t>-26,75; 1,41</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-13,53; 22,1</t>
+          <t>-15,18; 18,17</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-12,8; 22,07</t>
+          <t>-12,18; 25,54</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-30,44; 7,61</t>
+          <t>-30,64; 6,0</t>
         </is>
       </c>
     </row>
